--- a/data/trans_bre/POLIPATOLOGIA_5-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/POLIPATOLOGIA_5-Provincia-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,11; 7,08</t>
+          <t>0,13; 7,61</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,58; 9,57</t>
+          <t>0,51; 9,41</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,25; 13,82</t>
+          <t>3,98; 14,05</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,37; 5,99</t>
+          <t>0,89; 6,06</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-5,79; 452,01</t>
+          <t>-7,55; 529,15</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 307,16</t>
+          <t>1,67; 365,94</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>59,83; 451,88</t>
+          <t>55,79; 504,45</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>29,61; 536,27</t>
+          <t>22,25; 444,94</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,24; 11,66</t>
+          <t>5,34; 11,66</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,03; 7,73</t>
+          <t>0,99; 7,68</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,12; 6,92</t>
+          <t>2,21; 7,22</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,89; 11,11</t>
+          <t>4,45; 11,36</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>103,4; 582,44</t>
+          <t>113,43; 596,3</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,35; 223,23</t>
+          <t>10,25; 228,62</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>73,6; 840,92</t>
+          <t>74,27; 865,76</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>60,42; 268,08</t>
+          <t>52,99; 272,23</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 3,54</t>
+          <t>-0,85; 3,34</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,93; 9,24</t>
+          <t>1,53; 9,45</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,77; 8,27</t>
+          <t>2,01; 8,22</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,78; 9,1</t>
+          <t>0,49; 9,34</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-49,34; 823,56</t>
+          <t>-60,99; 713,69</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>26,54; 572,03</t>
+          <t>24,05; 688,39</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>33,23; 885,01</t>
+          <t>66,05; 1380,78</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,15; 88,9</t>
+          <t>2,2; 90,29</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 4,24</t>
+          <t>-0,67; 4,36</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,12; 14,55</t>
+          <t>5,89; 14,04</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,14; 12,55</t>
+          <t>4,22; 12,52</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,66; 7,39</t>
+          <t>-3,74; 7,69</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-35,42; 286,26</t>
+          <t>-26,85; 307,29</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>104,06; 572,85</t>
+          <t>96,68; 536,26</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>57,51; 347,49</t>
+          <t>54,71; 335,51</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-30,55; 84,82</t>
+          <t>-27,73; 85,22</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 7,38</t>
+          <t>-0,87; 7,08</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,05; 15,33</t>
+          <t>2,33; 14,98</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,69; 11,28</t>
+          <t>1,64; 11,91</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 10,87</t>
+          <t>-2,6; 10,99</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-41,42; 680,1</t>
+          <t>-50,41; 743,04</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,78; 251,32</t>
+          <t>19,57; 244,14</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,83; 470,47</t>
+          <t>13,06; 458,64</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-18,86; 144,04</t>
+          <t>-16,48; 151,05</t>
         </is>
       </c>
     </row>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,3; 7,6</t>
+          <t>2,07; 7,48</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 5,69</t>
+          <t>-2,18; 5,79</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 6,93</t>
+          <t>-0,43; 7,01</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5,02; 16,11</t>
+          <t>5,86; 16,21</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1185,17 +1185,17 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-33,65; 187,41</t>
+          <t>-37,22; 187,39</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-25,02; 292,36</t>
+          <t>-16,93; 315,29</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>25,92; 109,48</t>
+          <t>28,58; 112,68</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,44; 4,91</t>
+          <t>0,1; 4,63</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4,16; 9,82</t>
+          <t>3,85; 9,45</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,68; 9,51</t>
+          <t>3,65; 9,42</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12,48; 58,36</t>
+          <t>12,26; 62,2</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>7,96; 206,95</t>
+          <t>1,89; 205,07</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,67; 465,78</t>
+          <t>82,0; 407,07</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>57,52; 308,24</t>
+          <t>62,1; 314,02</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>123,69; 766,1</t>
+          <t>123,19; 769,47</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 4,59</t>
+          <t>-1,04; 4,68</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4,23; 8,77</t>
+          <t>4,32; 8,45</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4,92; 10,09</t>
+          <t>5,05; 10,24</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5,61; 12,84</t>
+          <t>5,5; 12,37</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-11,99; 78,5</t>
+          <t>-13,01; 82,11</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>156,92; 782,54</t>
+          <t>157,14; 742,27</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>107,88; 397,51</t>
+          <t>114,77; 406,64</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>78,53; 470,89</t>
+          <t>79,53; 467,39</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,26; 4,48</t>
+          <t>2,34; 4,31</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4,85; 7,27</t>
+          <t>4,95; 7,34</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5,12; 7,58</t>
+          <t>5,17; 7,62</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7,47; 27,74</t>
+          <t>7,48; 27,48</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>59,86; 150,39</t>
+          <t>60,5; 149,69</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>110,47; 214,81</t>
+          <t>115,67; 227,23</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>127,29; 242,88</t>
+          <t>126,79; 243,91</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>86,67; 371,67</t>
+          <t>88,56; 365,95</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/POLIPATOLOGIA_5-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/POLIPATOLOGIA_5-Provincia-trans_bre.xlsx
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>144,38%</t>
+          <t>141,53%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,13; 7,61</t>
+          <t>0,58; 7,47</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,51; 9,41</t>
+          <t>0,33; 9,28</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,98; 14,05</t>
+          <t>3,86; 14,25</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,89; 6,06</t>
+          <t>1,09; 5,95</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-7,55; 529,15</t>
+          <t>7,46; 531,64</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,67; 365,94</t>
+          <t>-4,73; 366,52</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>55,79; 504,45</t>
+          <t>51,88; 486,86</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>22,25; 444,94</t>
+          <t>17,83; 403,95</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7,99</t>
+          <t>7,59</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>139,95%</t>
+          <t>127,79%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,34; 11,66</t>
+          <t>4,99; 11,74</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,99; 7,68</t>
+          <t>1,0; 7,79</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,21; 7,22</t>
+          <t>1,91; 6,69</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,45; 11,36</t>
+          <t>4,26; 10,87</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>113,43; 596,3</t>
+          <t>90,87; 552,97</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,25; 228,62</t>
+          <t>9,67; 228,16</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>74,27; 865,76</t>
+          <t>73,25; 764,98</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>52,99; 272,23</t>
+          <t>52,19; 244,28</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5,06</t>
+          <t>4,54</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>41,69%</t>
+          <t>36,25%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 3,34</t>
+          <t>-0,57; 3,78</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,53; 9,45</t>
+          <t>1,96; 9,85</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,01; 8,22</t>
+          <t>2,1; 8,5</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,49; 9,34</t>
+          <t>0,31; 8,83</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-60,99; 713,69</t>
+          <t>-43,07; 1059,69</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>24,05; 688,39</t>
+          <t>24,55; 722,41</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>66,05; 1380,78</t>
+          <t>44,5; 1107,14</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,2; 90,29</t>
+          <t>1,73; 85,2</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2,49</t>
+          <t>6,19</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>63,96%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 4,36</t>
+          <t>-1,07; 4,46</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,89; 14,04</t>
+          <t>5,72; 13,72</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,22; 12,52</t>
+          <t>3,98; 12,7</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 7,69</t>
+          <t>1,65; 10,5</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-26,85; 307,29</t>
+          <t>-32,57; 360,99</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,68; 536,26</t>
+          <t>105,54; 506,51</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>54,71; 335,51</t>
+          <t>55,1; 356,28</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-27,73; 85,22</t>
+          <t>12,04; 148,35</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5,26</t>
+          <t>8,42</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>54,45%</t>
+          <t>95,49%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 7,08</t>
+          <t>-0,54; 7,28</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,33; 14,98</t>
+          <t>3,05; 16,21</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,64; 11,91</t>
+          <t>1,33; 11,74</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 10,99</t>
+          <t>4,13; 13,1</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-50,41; 743,04</t>
+          <t>-40,56; 742,26</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,57; 244,14</t>
+          <t>20,47; 286,13</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,06; 458,64</t>
+          <t>12,72; 424,02</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-16,48; 151,05</t>
+          <t>35,07; 203,11</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>10,87</t>
+          <t>10,99</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>64,17%</t>
+          <t>64,99%</t>
         </is>
       </c>
     </row>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,07; 7,48</t>
+          <t>2,37; 7,6</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 5,79</t>
+          <t>-1,94; 5,94</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 7,01</t>
+          <t>-0,9; 6,68</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5,86; 16,21</t>
+          <t>5,42; 16,42</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1185,17 +1185,17 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-37,22; 187,39</t>
+          <t>-33,7; 188,79</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-16,93; 315,29</t>
+          <t>-18,86; 320,74</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>28,58; 112,68</t>
+          <t>25,19; 111,16</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>32,03</t>
+          <t>13,29</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>339,51%</t>
+          <t>141,73%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,1; 4,63</t>
+          <t>0,5; 5,11</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,85; 9,45</t>
+          <t>3,87; 9,54</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,65; 9,42</t>
+          <t>3,72; 9,44</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12,26; 62,2</t>
+          <t>10,05; 16,73</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,89; 205,07</t>
+          <t>6,12; 232,64</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>82,0; 407,07</t>
+          <t>86,21; 427,09</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>62,1; 314,02</t>
+          <t>68,21; 315,91</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>123,19; 769,47</t>
+          <t>89,74; 215,72</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8,53</t>
+          <t>6,2</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>178,1%</t>
+          <t>98,74%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 4,68</t>
+          <t>-0,71; 4,76</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4,32; 8,45</t>
+          <t>4,04; 8,58</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5,05; 10,24</t>
+          <t>4,93; 10,42</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5,5; 12,37</t>
+          <t>3,61; 8,74</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-13,01; 82,11</t>
+          <t>-9,96; 79,97</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>157,14; 742,27</t>
+          <t>151,78; 763,04</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>114,77; 406,64</t>
+          <t>102,73; 411,88</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>79,53; 467,39</t>
+          <t>45,35; 167,2</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>12,74</t>
+          <t>7,99</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>160,16%</t>
+          <t>95,19%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,34; 4,31</t>
+          <t>2,25; 4,42</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4,95; 7,34</t>
+          <t>4,83; 7,36</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5,17; 7,62</t>
+          <t>5,05; 7,56</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7,48; 27,48</t>
+          <t>6,67; 9,21</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>60,5; 149,69</t>
+          <t>56,27; 145,6</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>115,67; 227,23</t>
+          <t>110,21; 221,93</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>126,79; 243,91</t>
+          <t>128,79; 250,31</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>88,56; 365,95</t>
+          <t>73,23; 120,11</t>
         </is>
       </c>
     </row>
